--- a/iaehi(EOIManila-v1)/iaehi(EOIManila-v1)/iaehi5-main/iaehi5-main/backend/EOIManila Users.xlsx
+++ b/iaehi(EOIManila-v1)/iaehi(EOIManila-v1)/iaehi5-main/iaehi5-main/backend/EOIManila Users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IAEHI\iaehi(Indo Philippino)\iaehi(EOIManila-v1)\iaehi(EOIManila-v1)\iaehi5-main\iaehi5-main\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF56972-0304-4827-A136-F0FB52464891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A102B683-07BD-4DC7-AAA0-DAE12B95636D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -626,6 +626,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:D4 E1:J4 K1:K4" numberStoredAsText="1"/>
   </ignoredErrors>
